--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1993</v>
+        <v>1921</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>66444000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>33339</v>
+        <v>34588</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>66444000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>33339</v>
+        <v>34588</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -29513,7 +29513,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>7380900</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>24685</v>
+        <v>24768</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>7380900</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>24685</v>
+        <v>24768</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         </is>
       </c>
       <c r="E513" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
         <v>7314600</v>
       </c>
       <c r="I513" s="5" t="n">
-        <v>24464</v>
+        <v>24546</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>7314600</v>
       </c>
       <c r="L513" s="5" t="n">
-        <v>24464</v>
+        <v>24546</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         </is>
       </c>
       <c r="E626" s="4" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F626" s="3" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>10129000</v>
       </c>
       <c r="I626" s="5" t="n">
-        <v>22020</v>
+        <v>21972</v>
       </c>
       <c r="J626" s="3" t="inlineStr">
         <is>
@@ -39546,7 +39546,7 @@
         <v>10129000</v>
       </c>
       <c r="L626" s="5" t="n">
-        <v>22020</v>
+        <v>21972</v>
       </c>
       <c r="M626" s="3" t="inlineStr">
         <is>
@@ -57960,9 +57960,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 1993呎 (4+房)
+          <t>A | 1921呎 (4+房)
 $6644万
-$33,339/呎
+$34,588/呎
 (24年-11月-14日)</t>
         </is>
       </c>
@@ -62233,9 +62233,9 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>A3 | 299呎 (1房)
+          <t>A3 | 298呎 (1房)
 $738万
-$24,685/呎
+$24,768/呎
 (24年-11月-11日)</t>
         </is>
       </c>
@@ -62689,9 +62689,9 @@
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>A3 | 299呎 (1房)
+          <t>A3 | 298呎 (1房)
 $731万
-$24,464/呎
+$24,546/呎
 (24年-11月-08日)</t>
         </is>
       </c>
@@ -64190,9 +64190,9 @@
       </c>
       <c r="R11" s="22" t="inlineStr">
         <is>
-          <t>F | 460呎 (2房)
+          <t>F | 461呎 (2房)
 $1013万
-$22,020/呎
+$21,972/呎
 (24年-11月-19日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -28583,7 +28583,7 @@
         </is>
       </c>
       <c r="E450" s="4" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>10839400</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>21295</v>
+        <v>21337</v>
       </c>
       <c r="J450" s="3" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>10839400</v>
       </c>
       <c r="L450" s="5" t="n">
-        <v>21295</v>
+        <v>21337</v>
       </c>
       <c r="M450" s="3" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         </is>
       </c>
       <c r="E675" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F675" s="3" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>7657300</v>
       </c>
       <c r="I675" s="5" t="n">
-        <v>25610</v>
+        <v>25696</v>
       </c>
       <c r="J675" s="3" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>7657300</v>
       </c>
       <c r="L675" s="5" t="n">
-        <v>25610</v>
+        <v>25696</v>
       </c>
       <c r="M675" s="3" t="inlineStr">
         <is>
@@ -62143,9 +62143,9 @@
       </c>
       <c r="H26" s="22" t="inlineStr">
         <is>
-          <t>A8 | 509呎 (2房)
+          <t>A8 | 508呎 (2房)
 $1084万
-$21,295/呎
+$21,337/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -64607,9 +64607,9 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>A3 | 299呎 (1房)
+          <t>A3 | 298呎 (1房)
 $766万
-$25,610/呎
+$25,696/呎
 (24年-11月-01日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1985</v>
+        <v>1914</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>69899000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>35214</v>
+        <v>36520</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>69899000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>35214</v>
+        <v>36520</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -58024,9 +58024,9 @@
       <c r="F20" s="20" t="inlineStr"/>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>B | 1985呎 (4+房)
+          <t>B | 1914呎 (4+房)
 $6990万
-$35,214/呎
+$36,520/呎
 (24年-11月-05日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -27963,7 +27963,7 @@
         </is>
       </c>
       <c r="E440" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>7410400</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>24784</v>
+        <v>24867</v>
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>7410400</v>
       </c>
       <c r="L440" s="5" t="n">
-        <v>24784</v>
+        <v>24867</v>
       </c>
       <c r="M440" s="3" t="inlineStr">
         <is>
@@ -62013,9 +62013,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>A5 | 299呎 (1房)
+          <t>A5 | 298呎 (1房)
 $741万
-$24,784/呎
+$24,867/呎
 (24年-11月-08日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -52361,7 +52361,7 @@
         </is>
       </c>
       <c r="E833" s="4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F833" s="3" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>5310800</v>
       </c>
       <c r="I833" s="5" t="n">
-        <v>22503</v>
+        <v>22408</v>
       </c>
       <c r="J833" s="3" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>5310800</v>
       </c>
       <c r="L833" s="5" t="n">
-        <v>22503</v>
+        <v>22408</v>
       </c>
       <c r="M833" s="3" t="inlineStr">
         <is>
@@ -66269,9 +66269,9 @@
       </c>
       <c r="M31" s="22" t="inlineStr">
         <is>
-          <t>B6 | 236呎 (开放式)
+          <t>B6 | 237呎 (开放式)
 $531万
-$22,503/呎
+$22,408/呎
 (24年-11月-05日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -10121,7 +10121,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>9347600</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>21390</v>
+        <v>21342</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>9347600</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>21390</v>
+        <v>21342</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         </is>
       </c>
       <c r="E651" s="4" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F651" s="3" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>10302100</v>
       </c>
       <c r="I651" s="5" t="n">
-        <v>21966</v>
+        <v>22013</v>
       </c>
       <c r="J651" s="3" t="inlineStr">
         <is>
@@ -41096,7 +41096,7 @@
         <v>10302100</v>
       </c>
       <c r="L651" s="5" t="n">
-        <v>21966</v>
+        <v>22013</v>
       </c>
       <c r="M651" s="3" t="inlineStr">
         <is>
@@ -59000,9 +59000,9 @@
       </c>
       <c r="L31" s="22" t="inlineStr">
         <is>
-          <t>B6 | 437呎 (2房)
+          <t>B6 | 438呎 (2房)
 $935万
-$21,390/呎
+$21,342/呎
 (24年-11月-04日)</t>
         </is>
       </c>
@@ -64440,9 +64440,9 @@
       </c>
       <c r="Q14" s="22" t="inlineStr">
         <is>
-          <t>E | 469呎 (2房)
+          <t>E | 468呎 (2房)
 $1030万
-$21,966/呎
+$22,013/呎
 (24年-11月-06日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -22631,7 +22631,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>11132100</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>21871</v>
+        <v>21914</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>11132100</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>21871</v>
+        <v>21914</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
@@ -61231,9 +61231,9 @@
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>A8 | 509呎 (2房)
+          <t>A8 | 508呎 (2房)
 $1113万
-$21,871/呎
+$21,914/呎
 (24年-10月-25日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>6811500</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>22630</v>
+        <v>22705</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>6811500</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>22630</v>
+        <v>22705</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>6636800</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>22049</v>
+        <v>22123</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>6636800</v>
       </c>
       <c r="L182" s="5" t="n">
-        <v>22049</v>
+        <v>22123</v>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
@@ -58288,9 +58288,9 @@
       </c>
       <c r="J23" s="22" t="inlineStr">
         <is>
-          <t>B3 | 301呎 (1房)
+          <t>B3 | 300呎 (1房)
 $681万
-$22,630/呎
+$22,705/呎
 (24年-10月-31日)</t>
         </is>
       </c>
@@ -59245,9 +59245,9 @@
       </c>
       <c r="J34" s="22" t="inlineStr">
         <is>
-          <t>B3 | 301呎 (1房)
+          <t>B3 | 300呎 (1房)
 $664万
-$22,049/呎
+$22,123/呎
 (24年-11月-01日)</t>
         </is>
       </c>
